--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1892-new.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1892-new.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF593F7-5DC7-42D7-90BA-F557E5BF275F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29545E72-063D-48AB-B4B9-40FD5639F32D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -982,7 +982,7 @@
       <name val="Arial Unicode MS"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1047,6 +1047,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -1076,7 +1082,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1311,6 +1317,15 @@
     <xf numFmtId="3" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2666,7 +2681,7 @@
       </c>
       <c r="AE18" s="73">
         <f>SUM(N19:AB19)</f>
-        <v>122463</v>
+        <v>121863</v>
       </c>
       <c r="AF18" s="73">
         <f>SUM(N20:AB20)</f>
@@ -2678,7 +2693,7 @@
       </c>
       <c r="AI18" s="73">
         <f>AE18-C18</f>
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="AJ18" s="73">
         <f>AF18-D18</f>
@@ -2746,7 +2761,7 @@
         <v>9315</v>
       </c>
       <c r="W19" s="5">
-        <v>7689</v>
+        <v>7089</v>
       </c>
       <c r="X19" s="5">
         <v>11118</v>
@@ -4358,7 +4373,7 @@
       </c>
       <c r="AE42" s="83">
         <f>SUM(AE2:AE39)</f>
-        <v>900605</v>
+        <v>900005</v>
       </c>
       <c r="AF42" s="83">
         <f>SUM(AF2:AF39)</f>
@@ -4370,7 +4385,7 @@
       </c>
       <c r="AI42" s="83">
         <f>C42-AE42</f>
-        <v>-618</v>
+        <v>-18</v>
       </c>
       <c r="AJ42" s="83">
         <f>D42-AF42</f>
@@ -6176,7 +6191,7 @@
       </c>
       <c r="AE68" s="73">
         <f>SUM(N69:AB69)</f>
-        <v>18960</v>
+        <v>20760</v>
       </c>
       <c r="AF68" s="73">
         <f>SUM(N70:AB70)</f>
@@ -6188,7 +6203,7 @@
       </c>
       <c r="AI68" s="73">
         <f>AE68-C68</f>
-        <v>-1800</v>
+        <v>0</v>
       </c>
       <c r="AJ68" s="73">
         <f>AF68-D68</f>
@@ -6243,8 +6258,8 @@
       <c r="R69" s="5">
         <v>2711</v>
       </c>
-      <c r="S69" s="5">
-        <v>2401</v>
+      <c r="S69" s="94">
+        <v>4201</v>
       </c>
       <c r="T69" s="5">
         <v>3414</v>
@@ -6570,7 +6585,7 @@
       </c>
       <c r="AE74" s="83">
         <f>SUM(AE43:AE73)</f>
-        <v>339048</v>
+        <v>340848</v>
       </c>
       <c r="AF74" s="83">
         <f>SUM(AF43:AF73)</f>
@@ -6582,7 +6597,7 @@
       </c>
       <c r="AI74" s="83">
         <f>C74-AE74</f>
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="AJ74" s="83">
         <f>D74-AF74</f>
@@ -8008,8 +8023,8 @@
       <c r="N94" s="15">
         <v>245075</v>
       </c>
-      <c r="O94" s="15">
-        <v>298050</v>
+      <c r="O94" s="94">
+        <v>258050</v>
       </c>
       <c r="P94" s="15">
         <v>280114</v>
@@ -8046,7 +8061,7 @@
       <c r="AB94" s="17"/>
       <c r="AD94" s="73">
         <f>SUM(N94:AB94)</f>
-        <v>2716577</v>
+        <v>2676577</v>
       </c>
       <c r="AE94" s="73">
         <f>SUM(N95:AB95)</f>
@@ -8058,7 +8073,7 @@
       </c>
       <c r="AH94" s="73">
         <f>AD94-B94</f>
-        <v>39990</v>
+        <v>-10</v>
       </c>
       <c r="AI94" s="73">
         <f>AE94-C94</f>
@@ -10689,8 +10704,8 @@
       <c r="A130" s="27" t="s">
         <v>133</v>
       </c>
-      <c r="B130" s="15">
-        <v>1595548</v>
+      <c r="B130" s="94">
+        <v>1593548</v>
       </c>
       <c r="C130" s="15">
         <v>74225</v>
@@ -10772,7 +10787,7 @@
       </c>
       <c r="AH130" s="73">
         <f>AD130-B130</f>
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="AI130" s="73">
         <f>AE130-C130</f>
@@ -10784,20 +10799,20 @@
       </c>
       <c r="AL130" s="74">
         <f>C130/B130*1000</f>
-        <v>46.520067086668654</v>
+        <v>46.578452610150428</v>
       </c>
       <c r="AM130" s="74">
         <f>D130/B130*1000</f>
-        <v>50.517439776177213</v>
+        <v>50.580842246358444</v>
       </c>
       <c r="AN130" s="79"/>
       <c r="AO130" s="74">
         <f>AL130-K130</f>
-        <v>2.0067086668653644E-2</v>
+        <v>7.845261015042837E-2</v>
       </c>
       <c r="AP130" s="74">
         <f>AM130-L130</f>
-        <v>1.7439776177212707E-2</v>
+        <v>8.0842246358443504E-2</v>
       </c>
     </row>
     <row r="131" spans="1:42" customFormat="1">
@@ -10911,11 +10926,11 @@
       <c r="B133" s="15">
         <v>2815860</v>
       </c>
-      <c r="C133" s="15">
-        <v>133579</v>
-      </c>
-      <c r="D133" s="15">
-        <v>137765</v>
+      <c r="C133" s="94">
+        <v>133279</v>
+      </c>
+      <c r="D133" s="94">
+        <v>137565</v>
       </c>
       <c r="E133" s="15">
         <v>138057</v>
@@ -10999,28 +11014,28 @@
       </c>
       <c r="AI133" s="73">
         <f>AE133-C133</f>
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="AJ133" s="73">
         <f>AF133-D133</f>
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="AL133" s="74">
         <f>C133/B133*1000</f>
-        <v>47.438082859233056</v>
+        <v>47.331543471621458</v>
       </c>
       <c r="AM133" s="74">
         <f>D133/B133*1000</f>
-        <v>48.924662447706915</v>
+        <v>48.853636189299188</v>
       </c>
       <c r="AN133" s="79"/>
       <c r="AO133" s="74">
         <f>AL133-K133</f>
-        <v>3.808285923305732E-2</v>
+        <v>-6.8456528378540327E-2</v>
       </c>
       <c r="AP133" s="74">
         <f>AM133-L133</f>
-        <v>2.4662447706916168E-2</v>
+        <v>-4.6363810700810859E-2</v>
       </c>
     </row>
     <row r="134" spans="1:42" customFormat="1">
@@ -11142,8 +11157,8 @@
       <c r="B136" s="15">
         <v>2983699</v>
       </c>
-      <c r="C136" s="15">
-        <v>127721</v>
+      <c r="C136" s="94">
+        <v>126721</v>
       </c>
       <c r="D136" s="15">
         <v>89300</v>
@@ -11236,7 +11251,7 @@
       </c>
       <c r="AI136" s="73">
         <f>AE136-C136</f>
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="AJ136" s="73">
         <f>AF136-D136</f>
@@ -11244,7 +11259,7 @@
       </c>
       <c r="AL136" s="74">
         <f>C136/B136*1000</f>
-        <v>42.806261623575303</v>
+        <v>42.471107172673918</v>
       </c>
       <c r="AM136" s="74">
         <f>D136/B136*1000</f>
@@ -11253,7 +11268,7 @@
       <c r="AN136" s="79"/>
       <c r="AO136" s="74">
         <f>AL136-K136</f>
-        <v>6.2616235753054639E-3</v>
+        <v>-0.32889282732607938</v>
       </c>
       <c r="AP136" s="74">
         <f>AM136-L136</f>
@@ -12423,11 +12438,11 @@
       </c>
       <c r="AE153" s="73">
         <f>SUM(N154:AB154)</f>
-        <v>111424</v>
+        <v>111418</v>
       </c>
       <c r="AF153" s="73">
         <f>SUM(N155:AB155)</f>
-        <v>145465</v>
+        <v>145459</v>
       </c>
       <c r="AH153" s="73">
         <f>AD153-B153</f>
@@ -12435,11 +12450,11 @@
       </c>
       <c r="AI153" s="73">
         <f>AE153-C153</f>
-        <v>-788</v>
+        <v>-794</v>
       </c>
       <c r="AJ153" s="73">
         <f>AF153-D153</f>
-        <v>-1051</v>
+        <v>-1057</v>
       </c>
       <c r="AL153" s="74">
         <f>C153/B153*1000</f>
@@ -12503,7 +12518,7 @@
         <v>8177</v>
       </c>
       <c r="W154" s="5">
-        <v>6857</v>
+        <v>6851</v>
       </c>
       <c r="X154" s="5"/>
       <c r="Y154" s="7"/>
@@ -12528,7 +12543,7 @@
       <c r="L155" s="53"/>
       <c r="M155" s="7"/>
       <c r="N155" s="5">
-        <v>21637</v>
+        <v>21631</v>
       </c>
       <c r="O155" s="5">
         <v>18488</v>
@@ -12817,8 +12832,8 @@
       <c r="R159" s="28">
         <v>102729</v>
       </c>
-      <c r="S159" s="28">
-        <v>89799</v>
+      <c r="S159" s="96">
+        <v>99795</v>
       </c>
       <c r="T159" s="28">
         <v>123586</v>
@@ -12843,7 +12858,7 @@
       <c r="AB159" s="30"/>
       <c r="AD159" s="73">
         <f>SUM(N159:AB159)</f>
-        <v>1427836</v>
+        <v>1437832</v>
       </c>
       <c r="AE159" s="73">
         <f>SUM(N160:AB160)</f>
@@ -12855,7 +12870,7 @@
       </c>
       <c r="AH159" s="73">
         <f>AD159-B159</f>
-        <v>-9995</v>
+        <v>1</v>
       </c>
       <c r="AI159" s="73">
         <f>AE159-C159</f>
@@ -12999,8 +13014,8 @@
       <c r="A162" s="27" t="s">
         <v>165</v>
       </c>
-      <c r="B162" s="28">
-        <v>1210770</v>
+      <c r="B162" s="96">
+        <v>1211270</v>
       </c>
       <c r="C162" s="28">
         <v>56143</v>
@@ -13080,7 +13095,7 @@
       </c>
       <c r="AH162" s="73">
         <f>AD162-B162</f>
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AI162" s="73">
         <f>AE162-C162</f>
@@ -13092,20 +13107,20 @@
       </c>
       <c r="AL162" s="74">
         <f>C162/B162*1000</f>
-        <v>46.369665584710553</v>
+        <v>46.35052465593963</v>
       </c>
       <c r="AM162" s="74">
         <f>D162/B162*1000</f>
-        <v>31.271835278376571</v>
+        <v>31.258926581191641</v>
       </c>
       <c r="AN162" s="79"/>
       <c r="AO162" s="74">
         <f>AL162-K162</f>
-        <v>-3.033441528944536E-2</v>
+        <v>-4.9475344060368798E-2</v>
       </c>
       <c r="AP162" s="74">
         <f>AM162-L162</f>
-        <v>-2.8164721623429756E-2</v>
+        <v>-4.1073418808359463E-2</v>
       </c>
     </row>
     <row r="163" spans="1:42" customFormat="1">
@@ -13212,8 +13227,8 @@
       <c r="A165" s="27" t="s">
         <v>168</v>
       </c>
-      <c r="B165" s="28">
-        <v>2968264</v>
+      <c r="B165" s="96">
+        <v>2908264</v>
       </c>
       <c r="C165" s="28">
         <v>126676</v>
@@ -13295,11 +13310,11 @@
       </c>
       <c r="AF165" s="73">
         <f>SUM(N167:AB167)</f>
-        <v>126958</v>
+        <v>127258</v>
       </c>
       <c r="AH165" s="73">
         <f>AD165-B165</f>
-        <v>-62100</v>
+        <v>-2100</v>
       </c>
       <c r="AI165" s="73">
         <f>AE165-C165</f>
@@ -13307,24 +13322,24 @@
       </c>
       <c r="AJ165" s="73">
         <f>AF165-D165</f>
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="AL165" s="74">
         <f>C165/B165*1000</f>
-        <v>42.676796942590009</v>
+        <v>43.557256150060653</v>
       </c>
       <c r="AM165" s="74">
         <f>D165/B165*1000</f>
-        <v>42.872871146232278</v>
+        <v>43.757375533995535</v>
       </c>
       <c r="AN165" s="79"/>
       <c r="AO165" s="74">
         <f>AL165-K165</f>
-        <v>-2.3203057409993733E-2</v>
+        <v>0.8572561500606497</v>
       </c>
       <c r="AP165" s="74">
         <f>AM165-L165</f>
-        <v>-2.7128853767720784E-2</v>
+        <v>0.8573755339955369</v>
       </c>
     </row>
     <row r="166" spans="1:42" customFormat="1">
@@ -13420,8 +13435,8 @@
       <c r="T167" s="7">
         <v>8625</v>
       </c>
-      <c r="U167" s="7">
-        <v>12547</v>
+      <c r="U167" s="96">
+        <v>12847</v>
       </c>
       <c r="V167" s="7">
         <v>5760</v>
@@ -14729,7 +14744,7 @@
       </c>
       <c r="AF185" s="73">
         <f>SUM(N187:AB187)</f>
-        <v>74590</v>
+        <v>72592</v>
       </c>
       <c r="AH185" s="73">
         <f>AD185-B185</f>
@@ -14741,7 +14756,7 @@
       </c>
       <c r="AJ185" s="73">
         <f>AF185-D185</f>
-        <v>1998</v>
+        <v>0</v>
       </c>
       <c r="AL185" s="74">
         <f>C185/B185*1000</f>
@@ -14854,8 +14869,8 @@
       <c r="R187" s="7">
         <v>4288</v>
       </c>
-      <c r="S187" s="7">
-        <v>6655</v>
+      <c r="S187" s="96">
+        <v>4655</v>
       </c>
       <c r="T187" s="7">
         <v>3487</v>
@@ -14863,8 +14878,8 @@
       <c r="U187" s="7">
         <v>4007</v>
       </c>
-      <c r="V187" s="7">
-        <v>4763</v>
+      <c r="V187" s="96">
+        <v>4765</v>
       </c>
       <c r="W187" s="7">
         <v>5053</v>
@@ -15153,27 +15168,27 @@
       <c r="AB191" s="26"/>
       <c r="AD191" s="83">
         <f>SUM(AD85:AD190)</f>
-        <v>65612628</v>
+        <v>65582624</v>
       </c>
       <c r="AE191" s="83">
         <f>SUM(AE85:AE190)</f>
-        <v>2939372</v>
+        <v>2939366</v>
       </c>
       <c r="AF191" s="83">
         <f>SUM(AF85:AF190)</f>
-        <v>2728598</v>
+        <v>2726894</v>
       </c>
       <c r="AH191" s="83">
         <f>B191-AD191</f>
-        <v>411511</v>
+        <v>441515</v>
       </c>
       <c r="AI191" s="83">
         <f>C191-AE191</f>
-        <v>1620</v>
+        <v>1626</v>
       </c>
       <c r="AJ191" s="83">
         <f>D191-AF191</f>
-        <v>-455</v>
+        <v>1249</v>
       </c>
       <c r="AL191" s="82">
         <f>C191/B191*1000</f>
@@ -15449,27 +15464,27 @@
       <c r="AB195" s="26"/>
       <c r="AD195" s="84">
         <f>SUM(AD42, AD74, AD84, AD191, AD192)</f>
-        <v>99836775</v>
+        <v>99806771</v>
       </c>
       <c r="AE195" s="84">
         <f>SUM(AE42, AE74, AE84, AE191, AE192)</f>
-        <v>4362740</v>
+        <v>4363934</v>
       </c>
       <c r="AF195" s="84">
         <f>SUM(AF42, AF74, AF84, AF191, AF192)</f>
-        <v>3825781</v>
+        <v>3824077</v>
       </c>
       <c r="AH195" s="83">
         <f>B195-AD195</f>
-        <v>414735</v>
+        <v>444739</v>
       </c>
       <c r="AI195" s="83">
         <f>C195-AE195</f>
-        <v>2802</v>
+        <v>1608</v>
       </c>
       <c r="AJ195" s="83">
         <f>D195-AF195</f>
-        <v>-500</v>
+        <v>1204</v>
       </c>
       <c r="AL195" s="82">
         <f>C195/B195*1000</f>
@@ -16167,8 +16182,8 @@
       <c r="L206" s="56">
         <v>61.8</v>
       </c>
-      <c r="N206" s="33">
-        <v>119258</v>
+      <c r="N206" s="95">
+        <v>219258</v>
       </c>
       <c r="O206" s="33">
         <v>173665</v>
@@ -16200,11 +16215,11 @@
       <c r="AB206" s="33"/>
       <c r="AD206" s="73">
         <f>SUM(N206:AB206)</f>
-        <v>1485510</v>
+        <v>1585510</v>
       </c>
       <c r="AE206" s="73">
         <f>SUM(N207:AB207)</f>
-        <v>95619</v>
+        <v>95789</v>
       </c>
       <c r="AF206" s="73">
         <f>SUM(N208:AB208)</f>
@@ -16213,11 +16228,11 @@
       <c r="AG206"/>
       <c r="AH206" s="73">
         <f>AD206-B206</f>
-        <v>-100000</v>
+        <v>0</v>
       </c>
       <c r="AI206" s="73">
         <f>AE206-C206</f>
-        <v>-206</v>
+        <v>-36</v>
       </c>
       <c r="AJ206" s="73">
         <f>AF206-D206</f>
@@ -16253,8 +16268,8 @@
       <c r="N207" s="2">
         <v>11808</v>
       </c>
-      <c r="O207" s="2">
-        <v>10349</v>
+      <c r="O207" s="95">
+        <v>10549</v>
       </c>
       <c r="P207" s="2">
         <v>13717</v>
@@ -16271,8 +16286,8 @@
       <c r="T207" s="2">
         <v>16676</v>
       </c>
-      <c r="U207" s="2">
-        <v>1543</v>
+      <c r="U207" s="95">
+        <v>1513</v>
       </c>
       <c r="W207" s="2"/>
       <c r="X207" s="2"/>
@@ -16880,8 +16895,8 @@
       <c r="A218" s="32" t="s">
         <v>221</v>
       </c>
-      <c r="B218" s="33">
-        <v>794992</v>
+      <c r="B218" s="95">
+        <v>834734</v>
       </c>
       <c r="C218" s="33">
         <v>27519</v>
@@ -16925,8 +16940,8 @@
       <c r="Q218" s="33">
         <v>102231</v>
       </c>
-      <c r="R218" s="33">
-        <v>79415</v>
+      <c r="R218" s="95">
+        <v>179415</v>
       </c>
       <c r="S218" s="33">
         <v>70421</v>
@@ -16948,7 +16963,7 @@
       <c r="AB218" s="33"/>
       <c r="AD218" s="73">
         <f>SUM(N218:AB218)</f>
-        <v>734734</v>
+        <v>834734</v>
       </c>
       <c r="AE218" s="73">
         <f>SUM(N219:AB219)</f>
@@ -16961,7 +16976,7 @@
       <c r="AG218"/>
       <c r="AH218" s="73">
         <f>AD218-B218</f>
-        <v>-60258</v>
+        <v>0</v>
       </c>
       <c r="AI218" s="73">
         <f>AE218-C218</f>
@@ -16974,20 +16989,20 @@
       <c r="AK218"/>
       <c r="AL218" s="74">
         <f>C218/B218*1000</f>
-        <v>34.615442671121215</v>
+        <v>32.967388413554495</v>
       </c>
       <c r="AM218" s="74">
         <f>D218/B218*1000</f>
-        <v>26.668192887475598</v>
+        <v>25.398510184082596</v>
       </c>
       <c r="AN218" s="79"/>
       <c r="AO218" s="74">
         <f>AL218-K218</f>
-        <v>-2.8845573288787847</v>
+        <v>-4.5326115864455048</v>
       </c>
       <c r="AP218" s="74">
         <f>AM218-L218</f>
-        <v>-2.2318071125244003</v>
+        <v>-3.5014898159174024</v>
       </c>
     </row>
     <row r="219" spans="1:42">
@@ -17295,11 +17310,11 @@
       <c r="AB224" s="35"/>
       <c r="AD224" s="86">
         <f>SUM(AD196:AD223)</f>
-        <v>7764023</v>
+        <v>7964023</v>
       </c>
       <c r="AE224" s="86">
         <f>SUM(AE196:AE223)</f>
-        <v>306745</v>
+        <v>306915</v>
       </c>
       <c r="AF224" s="86">
         <f>SUM(AF196:AF223)</f>
@@ -17307,11 +17322,11 @@
       </c>
       <c r="AH224" s="83">
         <f>B224-AD224</f>
-        <v>100179</v>
+        <v>-99821</v>
       </c>
       <c r="AI224" s="83">
         <f>C224-AE224</f>
-        <v>-23463</v>
+        <v>-23633</v>
       </c>
       <c r="AJ224" s="83">
         <f>D224-AF224</f>
@@ -17440,8 +17455,8 @@
         <v>39.5</v>
       </c>
       <c r="M226" s="5"/>
-      <c r="N226" s="37">
-        <v>80600</v>
+      <c r="N226" s="94">
+        <v>86600</v>
       </c>
       <c r="O226" s="37">
         <v>88093</v>
@@ -17469,7 +17484,7 @@
       <c r="AB226" s="40"/>
       <c r="AD226" s="73">
         <f>SUM(N226:AB226)</f>
-        <v>472783</v>
+        <v>478783</v>
       </c>
       <c r="AE226" s="73">
         <f>SUM(N227:AB227)</f>
@@ -17481,7 +17496,7 @@
       </c>
       <c r="AH226" s="73">
         <f>AD226-B226</f>
-        <v>-6003</v>
+        <v>-3</v>
       </c>
       <c r="AI226" s="73">
         <f>AE226-C226</f>
@@ -18426,8 +18441,8 @@
       <c r="B241" s="37">
         <v>1414440</v>
       </c>
-      <c r="C241" s="37">
-        <v>77947</v>
+      <c r="C241" s="94">
+        <v>77447</v>
       </c>
       <c r="D241" s="37">
         <v>62123</v>
@@ -18502,7 +18517,7 @@
       </c>
       <c r="AI241" s="73">
         <f>AE241-C241</f>
-        <v>-500</v>
+        <v>0</v>
       </c>
       <c r="AJ241" s="73">
         <f>AF241-D241</f>
@@ -18510,7 +18525,7 @@
       </c>
       <c r="AL241" s="74">
         <f>C241/B241*1000</f>
-        <v>55.108028619100139</v>
+        <v>54.754531828851</v>
       </c>
       <c r="AM241" s="74">
         <f>D241/B241*1000</f>
@@ -18519,7 +18534,7 @@
       <c r="AN241" s="79"/>
       <c r="AO241" s="74">
         <f>AL241-K241</f>
-        <v>8.028619100137746E-3</v>
+        <v>-0.34546817114900108</v>
       </c>
       <c r="AP241" s="74">
         <f>AM241-L241</f>
@@ -19029,7 +19044,7 @@
       <c r="AB250" s="42"/>
       <c r="AD250" s="83">
         <f>SUM(AD225:AD249)</f>
-        <v>4850899</v>
+        <v>4856899</v>
       </c>
       <c r="AE250" s="83">
         <f>SUM(AE225:AE249)</f>
@@ -19041,7 +19056,7 @@
       </c>
       <c r="AH250" s="83">
         <f>B250-AD250</f>
-        <v>6003</v>
+        <v>3</v>
       </c>
       <c r="AI250" s="83">
         <f>C250-AE250</f>
@@ -20598,27 +20613,27 @@
       <c r="AB275" s="47"/>
       <c r="AD275" s="84">
         <f>SUM(AD195, AD224, AD250, AD274)</f>
-        <v>118767887</v>
+        <v>118943883</v>
       </c>
       <c r="AE275" s="84">
         <f>SUM(AE195, AE224, AE250, AE274)</f>
-        <v>4972822</v>
+        <v>4974186</v>
       </c>
       <c r="AF275" s="84">
         <f>SUM(AF195, AF224, AF250, AF274)</f>
-        <v>4404471</v>
+        <v>4402767</v>
       </c>
       <c r="AH275" s="83">
         <f t="shared" si="6"/>
-        <v>520917</v>
+        <v>344921</v>
       </c>
       <c r="AI275" s="83">
         <f t="shared" si="6"/>
-        <v>3564</v>
+        <v>2200</v>
       </c>
       <c r="AJ275" s="83">
         <f t="shared" si="6"/>
-        <v>-570</v>
+        <v>1134</v>
       </c>
       <c r="AK275"/>
       <c r="AL275" s="82">
